--- a/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2024.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:36</t>
+    <t xml:space="preserve">2026-09-09 21:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2024.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:34</t>
+    <t xml:space="preserve">2026-09-16 21:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2024.xlsx
@@ -6,55 +6,74 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Serie" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Serie_anual" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Serie'!$A$1:$B$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Serie_anual'!$A$1:$B$8</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t xml:space="preserve">Territorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hombres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mujeres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de creación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01 13:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT - MDSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagen asociada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plot_nacional_serie_d_enveje_a_2024.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Índice de envejecimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile (Nacional)</t>
+  </si>
   <si>
     <t xml:space="preserve">Año</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha de creación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16 21:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIT - MDSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagen asociada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plot_nacional_serie_d_enveje_a_2024.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Índice de envejecimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unidad territorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chile (Nacional)</t>
   </si>
   <si>
     <t xml:space="preserve">2024</t>
@@ -422,8 +441,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -433,65 +455,35 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>2018</v>
+      <c r="A2" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>84.27</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>87.85</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>96.74</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>107.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>111.05</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>116.85</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="C2" s="2" t="n">
         <v>125.31</v>
       </c>
+      <c r="D2" s="2" t="n">
+        <v>112.01</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>139.11</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B8"/>
+  <autoFilter ref="A1:E2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -508,62 +500,142 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>84.27</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>87.85</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>96.74</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>107.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>111.05</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>116.85</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>125.31</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2024.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 13:04</t>
+    <t xml:space="preserve">2026-10-02 23:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_d_enveje_a_2024.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 23:44</t>
+    <t xml:space="preserve">2026-10-05 05:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
